--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -151,24 +151,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -843,13 +825,13 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>7</v>
@@ -897,13 +879,13 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -920,13 +902,13 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -974,13 +956,13 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -997,13 +979,13 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -1051,13 +1033,13 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1074,13 +1056,13 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1128,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1151,13 +1133,13 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1205,13 +1187,13 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1228,13 +1210,13 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>7</v>
@@ -1282,13 +1264,13 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1305,13 +1287,13 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>7</v>
@@ -1359,13 +1341,13 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1382,13 +1364,13 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1436,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1459,13 +1441,13 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>7</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1513,13 +1495,13 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1536,13 +1518,13 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1590,13 +1572,13 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1613,13 +1595,13 @@
         <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1667,13 +1649,13 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1690,13 +1672,13 @@
         <v>8</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -1744,13 +1726,13 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1767,13 +1749,13 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -1821,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1844,13 +1826,13 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1898,13 +1880,13 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1921,13 +1903,13 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -1975,13 +1957,13 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -1998,13 +1980,13 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -2052,13 +2034,13 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2075,13 +2057,13 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>7</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2129,13 +2111,13 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2152,13 +2134,13 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2206,13 +2188,13 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2229,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2283,13 +2265,13 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2306,13 +2288,13 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2360,13 +2342,13 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2493,13 +2475,13 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>84</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>92</v>
@@ -2552,13 +2534,13 @@
         <v>96.7</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>84</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>92</v>
@@ -2611,13 +2593,13 @@
         <v>93.3</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>84</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G6">
         <v>92</v>
@@ -2670,13 +2652,13 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>88</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>92</v>
@@ -2729,13 +2711,13 @@
         <v>90</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G8">
         <v>92</v>
@@ -2788,13 +2770,13 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>96</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -2847,13 +2829,13 @@
         <v>90</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>80</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G10">
         <v>92</v>
@@ -2906,13 +2888,13 @@
         <v>96.7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>92</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>92</v>
@@ -2965,13 +2947,13 @@
         <v>96.7</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>84</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>92</v>
@@ -3024,13 +3006,13 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>88</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>92</v>
@@ -3083,13 +3065,13 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>96</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>92</v>
@@ -3142,13 +3124,13 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>92</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>92</v>
@@ -3201,13 +3183,13 @@
         <v>93.3</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>88</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G16">
         <v>92</v>
@@ -3260,13 +3242,13 @@
         <v>93.3</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G17">
         <v>76</v>
@@ -3319,13 +3301,13 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>96</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>92</v>
@@ -3378,13 +3360,13 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>92</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>92</v>
@@ -3437,13 +3419,13 @@
         <v>96.7</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>92</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>92</v>
@@ -3496,13 +3478,13 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>96</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>92</v>
@@ -3555,13 +3537,13 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>88</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G22">
         <v>92</v>
@@ -3614,13 +3596,13 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>96</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>92</v>
@@ -3674,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -3714,307 +3696,193 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>35</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>45</v>
       </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
       <c r="C3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>90</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>95</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10">
-        <v>20</v>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>35</v>
-      </c>
-      <c r="G10">
-        <v>65</v>
-      </c>
-      <c r="H10">
-        <v>6</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>18</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>90</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>7.5</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>19</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>95</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>8.6</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13">
-        <v>20</v>
-      </c>
-      <c r="D13">
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>7.3</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -4025,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4034,862 +3902,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920336</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920336</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920337</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920337</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920263</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920263</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920340</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920340</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920340</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920341</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920341</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920344</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920344</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920345</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920345</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920381</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920381</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920347</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920347</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920348</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920348</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920349</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920349</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920350</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920350</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920352</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920352</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920354</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920354</v>
-      </c>
-      <c r="B30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920354</v>
-      </c>
-      <c r="B31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920355</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920355</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920382</v>
-      </c>
-      <c r="B34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920382</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330050470596</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330050470596</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920356</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920356</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920357</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920357</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920383</v>
-      </c>
-      <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920383</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4908,16 +3936,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>42</v>
@@ -4925,240 +3953,240 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920340</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920354</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
         <v>87</v>
       </c>
-      <c r="D3" t="s">
-        <v>105</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920263</v>
+        <v>20330051920341</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920341</v>
+        <v>20330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920344</v>
+        <v>20330051920345</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920381</v>
+        <v>20330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920347</v>
+        <v>20330051920348</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920348</v>
+        <v>20330051920349</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920349</v>
+        <v>20330051920350</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920350</v>
+        <v>20330051920352</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920352</v>
+        <v>20330051920354</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5166,16 +4194,16 @@
         <v>20330051920355</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5183,16 +4211,16 @@
         <v>20330051920382</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5200,16 +4228,16 @@
         <v>19330050470596</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5217,16 +4245,16 @@
         <v>20330051920356</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5234,16 +4262,16 @@
         <v>20330051920357</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5251,16 +4279,16 @@
         <v>20330051920383</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5270,7 +4298,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5279,16 +4307,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5302,324 +4330,278 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920341</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920263</v>
+        <v>20330051920345</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920263</v>
+        <v>20330051920381</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920344</v>
+        <v>20330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920344</v>
+        <v>20330051920349</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920345</v>
+        <v>20330051920350</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920345</v>
+        <v>20330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
         <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920348</v>
+        <v>19330050470596</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920348</v>
+        <v>20330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920355</v>
+        <v>20330051920357</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920355</v>
+        <v>20330051920383</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920382</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920382</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -153,13 +153,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -3763,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -3795,7 +3801,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -3827,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -3859,7 +3865,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -3902,16 +3908,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -3936,16 +3942,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>42</v>
@@ -3956,13 +3962,13 @@
         <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3973,13 +3979,13 @@
         <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3990,13 +3996,13 @@
         <v>20330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4007,13 +4013,13 @@
         <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4024,13 +4030,13 @@
         <v>20330051920341</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4041,13 +4047,13 @@
         <v>20330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4058,13 +4064,13 @@
         <v>20330051920345</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4075,13 +4081,13 @@
         <v>20330051920381</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4092,13 +4098,13 @@
         <v>20330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4109,13 +4115,13 @@
         <v>20330051920348</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4126,13 +4132,13 @@
         <v>20330051920349</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4143,13 +4149,13 @@
         <v>20330051920350</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4160,13 +4166,13 @@
         <v>20330051920352</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4177,13 +4183,13 @@
         <v>20330051920354</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4194,13 +4200,13 @@
         <v>20330051920355</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4211,13 +4217,13 @@
         <v>20330051920382</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4228,13 +4234,13 @@
         <v>19330050470596</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4245,13 +4251,13 @@
         <v>20330051920356</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4262,13 +4268,13 @@
         <v>20330051920357</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4279,13 +4285,13 @@
         <v>20330051920383</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4307,16 +4313,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4333,13 +4339,13 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -4356,13 +4362,13 @@
         <v>20330051920341</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4379,13 +4385,13 @@
         <v>20330051920345</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -4402,13 +4408,13 @@
         <v>20330051920381</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4425,13 +4431,13 @@
         <v>20330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -4448,13 +4454,13 @@
         <v>20330051920349</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4471,13 +4477,13 @@
         <v>20330051920350</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4494,13 +4500,13 @@
         <v>20330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4517,13 +4523,13 @@
         <v>19330050470596</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4540,13 +4546,13 @@
         <v>20330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4563,13 +4569,13 @@
         <v>20330051920357</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4586,13 +4592,13 @@
         <v>20330051920383</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>

--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -165,12 +164,12 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -183,99 +182,48 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
     <t>NAMIGTLE</t>
   </si>
   <si>
     <t>ROMAN</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -285,49 +233,22 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>CESAR</t>
+    <t>ELIEL</t>
   </si>
   <si>
     <t>ISYSS MONSERRATH</t>
   </si>
   <si>
-    <t>MARIAM GUADALUPE</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
     <t>EDGAR DANIEL</t>
   </si>
   <si>
     <t>EVELYN</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>ANGEL ALDAHIR</t>
   </si>
   <si>
     <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
@@ -346,6 +267,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -398,11 +322,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,10 +768,10 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -855,10 +780,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -891,10 +816,10 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -920,10 +845,10 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -932,10 +857,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -956,10 +881,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -971,7 +896,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -997,10 +922,10 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1009,10 +934,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1033,7 +958,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1045,10 +970,10 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1074,10 +999,10 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1086,10 +1011,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1113,7 +1038,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1151,10 +1076,10 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1163,10 +1088,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1190,7 +1115,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1228,10 +1153,10 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1240,10 +1165,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1267,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1305,10 +1230,10 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1317,10 +1242,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1341,10 +1266,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1356,7 +1281,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1382,10 +1307,10 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1394,10 +1319,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1459,10 +1384,10 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1471,10 +1396,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1498,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1507,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1536,10 +1461,10 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1548,10 +1473,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1572,10 +1497,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1587,7 +1512,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1613,10 +1538,10 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1625,10 +1550,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1649,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1661,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1690,10 +1615,10 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1702,10 +1627,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1738,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1767,10 +1692,10 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1779,10 +1704,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1803,10 +1728,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1818,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1844,10 +1769,10 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1856,10 +1781,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1880,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -1921,10 +1846,10 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -1933,10 +1858,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1960,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -1972,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1998,10 +1923,10 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2010,10 +1935,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2075,10 +2000,10 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2087,10 +2012,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2111,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2152,10 +2077,10 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2164,10 +2089,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2200,7 +2125,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2229,10 +2154,10 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2241,10 +2166,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2268,7 +2193,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2306,10 +2231,10 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2318,10 +2243,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2345,7 +2270,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2493,10 +2418,10 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2505,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2552,10 +2477,10 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2564,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2611,10 +2536,10 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2623,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2670,10 +2595,10 @@
         <v>92</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2682,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2729,10 +2654,10 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2741,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2788,10 +2713,10 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2800,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2847,10 +2772,10 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2859,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2906,10 +2831,10 @@
         <v>92</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2918,10 +2843,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2965,10 +2890,10 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2977,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3024,10 +2949,10 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3036,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3083,10 +3008,10 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3095,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3142,10 +3067,10 @@
         <v>92</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3154,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3201,10 +3126,10 @@
         <v>92</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3213,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3260,10 +3185,10 @@
         <v>76</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3272,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3319,10 +3244,10 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3331,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -3378,10 +3303,10 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3390,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -3437,10 +3362,10 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3449,10 +3374,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -3496,10 +3421,10 @@
         <v>92</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3508,10 +3433,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -3555,10 +3480,10 @@
         <v>92</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3567,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -3614,10 +3539,10 @@
         <v>92</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3626,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3666,6 +3591,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3711,24 +3638,24 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>35</v>
-      </c>
-      <c r="G2">
-        <v>65</v>
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45</v>
+      </c>
+      <c r="G2" s="2">
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3748,19 +3675,19 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>90</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>10</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3780,10 +3707,10 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>90</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>10</v>
       </c>
       <c r="H4">
@@ -3792,7 +3719,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3807,30 +3734,30 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>95</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -3839,30 +3766,30 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>90</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -3876,19 +3803,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3933,378 +3860,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920336</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920337</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920263</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920340</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920341</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920344</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920345</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920381</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920347</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920348</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920349</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920350</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920352</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920354</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920355</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920382</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>19330050470596</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920356</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920357</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920383</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4336,22 +3892,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4359,22 +3915,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920341</v>
+        <v>20330051920345</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4382,22 +3938,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920345</v>
+        <v>20330051920341</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4408,13 +3964,13 @@
         <v>20330051920381</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4431,13 +3987,13 @@
         <v>20330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -4454,13 +4010,13 @@
         <v>20330051920349</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4477,13 +4033,13 @@
         <v>20330051920350</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4497,16 +4053,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920352</v>
+        <v>19330050470596</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4520,16 +4076,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330050470596</v>
+        <v>20330051920356</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4543,16 +4099,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920356</v>
+        <v>20330051920357</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4566,16 +4122,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920357</v>
+        <v>20330051920383</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4584,29 +4140,6 @@
         <v>44</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920383</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -774,10 +774,10 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -810,10 +810,10 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -851,10 +851,10 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -890,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -928,10 +928,10 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -967,7 +967,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1005,10 +1005,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1082,10 +1082,10 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1159,10 +1159,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1275,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1313,10 +1313,10 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1390,10 +1390,10 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1467,10 +1467,10 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1544,10 +1544,10 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1621,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1698,10 +1698,10 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -1737,7 +1737,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1775,10 +1775,10 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1852,10 +1852,10 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -1929,10 +1929,10 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2006,10 +2006,10 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2083,10 +2083,10 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2160,10 +2160,10 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2237,10 +2237,10 @@
         <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2276,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2424,10 +2424,10 @@
         <v>93.3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>88</v>
@@ -2483,10 +2483,10 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -2542,10 +2542,10 @@
         <v>96.7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>68</v>
@@ -2601,10 +2601,10 @@
         <v>96.7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -2660,10 +2660,10 @@
         <v>93.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>92</v>
@@ -2719,10 +2719,10 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -2778,10 +2778,10 @@
         <v>90</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -2837,10 +2837,10 @@
         <v>96.7</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -2896,10 +2896,10 @@
         <v>96.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -2955,10 +2955,10 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3014,10 +3014,10 @@
         <v>96.7</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -3073,10 +3073,10 @@
         <v>96.7</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3132,10 +3132,10 @@
         <v>93.3</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>88</v>
@@ -3191,10 +3191,10 @@
         <v>96.7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>80</v>
@@ -3250,10 +3250,10 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>88</v>
@@ -3309,10 +3309,10 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -3368,10 +3368,10 @@
         <v>93.3</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -3427,10 +3427,10 @@
         <v>93.3</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>88</v>
@@ -3486,10 +3486,10 @@
         <v>96.7</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -3545,10 +3545,10 @@
         <v>96.7</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>80</v>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -2409,49 +2409,49 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L4">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2468,49 +2468,49 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2527,49 +2527,49 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="F6">
         <v>92</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="I6">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L6">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M6">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2586,49 +2586,49 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2645,49 +2645,49 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>70.8</v>
       </c>
       <c r="F8">
         <v>80</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>63.3</v>
+        <v>71.7</v>
       </c>
       <c r="I8">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="J8">
-        <v>120</v>
+        <v>65.5</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L8">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M8">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2704,13 +2704,13 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
       </c>
       <c r="G9">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -2719,7 +2719,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -2728,25 +2728,25 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2763,49 +2763,49 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="F10">
         <v>76</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I10">
         <v>90</v>
       </c>
       <c r="J10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M10">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2822,49 +2822,49 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F11">
         <v>100</v>
       </c>
       <c r="G11">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I11">
         <v>96.7</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2881,49 +2881,49 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I12">
         <v>96.7</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2940,13 +2940,13 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -2955,34 +2955,34 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2999,22 +2999,22 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I14">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3023,25 +3023,25 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3058,49 +3058,49 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F15">
         <v>100</v>
       </c>
       <c r="G15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3117,49 +3117,49 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F16">
         <v>84</v>
       </c>
       <c r="G16">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I16">
         <v>93.3</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L16">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M16">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3176,49 +3176,49 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>76</v>
+        <v>79.2</v>
       </c>
       <c r="F17">
         <v>68</v>
       </c>
       <c r="G17">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H17">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I17">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="L17">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M17">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3235,13 +3235,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -3250,34 +3250,34 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3294,13 +3294,13 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>100</v>
@@ -3309,34 +3309,34 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3353,49 +3353,49 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F20">
         <v>100</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I20">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3412,49 +3412,49 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M21">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3471,49 +3471,49 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F22">
         <v>88</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M22">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3530,49 +3530,49 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I23">
+        <v>98.3</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
+        <v>90</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>96.7</v>
       </c>
-      <c r="J23">
-        <v>120</v>
-      </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
-        <v>80</v>
-      </c>
-      <c r="M23">
-        <v>104</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
       <c r="O23">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6APM - Estadisticos 20222.xlsx
+++ b/grupos/6APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="60">
   <si>
     <t>Materia</t>
   </si>
@@ -152,6 +152,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
@@ -161,15 +167,9 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -182,85 +182,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
   </si>
 </sst>
 </file>
@@ -786,31 +723,31 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -863,22 +800,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -896,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,22 +877,22 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -967,13 +904,13 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1017,25 +954,25 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1050,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1094,40 +1031,40 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1171,25 +1108,25 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1204,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1248,40 +1185,40 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1325,22 +1262,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1355,10 +1292,10 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1402,22 +1339,22 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1435,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1479,22 +1416,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1556,22 +1493,22 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1586,10 +1523,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1633,22 +1570,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1666,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1710,31 +1647,31 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>8</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1743,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1787,22 +1724,22 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1814,10 +1751,10 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1864,25 +1801,25 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -1941,22 +1878,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2018,22 +1955,22 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2051,7 +1988,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2095,40 +2032,40 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2172,22 +2109,22 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2205,7 +2142,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2249,28 +2186,28 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2282,7 +2219,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2436,19 +2373,19 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O4">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>93.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R4">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2495,16 +2432,16 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O5">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>93.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -2554,19 +2491,19 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>91.7</v>
+        <v>88.5</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>93.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="R6">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2616,13 +2553,13 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -2672,22 +2609,22 @@
         <v>89.8</v>
       </c>
       <c r="N8">
-        <v>71.7</v>
+        <v>76</v>
       </c>
       <c r="O8">
-        <v>91.7</v>
+        <v>92.7</v>
       </c>
       <c r="P8">
-        <v>65.5</v>
+        <v>76.3</v>
       </c>
       <c r="Q8">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="R8">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="S8">
-        <v>89.8</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2740,7 +2677,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -2790,22 +2727,22 @@
         <v>89.8</v>
       </c>
       <c r="N10">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="O10">
+        <v>92.7</v>
+      </c>
+      <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>91.3</v>
+      </c>
+      <c r="R10">
+        <v>92.5</v>
+      </c>
+      <c r="S10">
         <v>93.3</v>
-      </c>
-      <c r="O10">
-        <v>90</v>
-      </c>
-      <c r="P10">
-        <v>100</v>
-      </c>
-      <c r="Q10">
-        <v>91.8</v>
-      </c>
-      <c r="R10">
-        <v>88</v>
-      </c>
-      <c r="S10">
-        <v>89.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2849,16 +2786,16 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="O11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -2908,16 +2845,16 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="O12">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -2976,7 +2913,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3026,10 +2963,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="O14">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3085,16 +3022,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="O15">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3144,19 +3081,19 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="O16">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R16">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3203,22 +3140,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O17">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>89.8</v>
+        <v>91.3</v>
       </c>
       <c r="R17">
-        <v>74</v>
+        <v>83.8</v>
       </c>
       <c r="S17">
-        <v>81.59999999999999</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3271,10 +3208,10 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R18">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3330,7 +3267,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -3380,16 +3317,16 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -3442,16 +3379,16 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R21">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3501,16 +3438,16 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R22">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -3557,10 +3494,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O23">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -3569,7 +3506,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -3629,7 +3566,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -3638,19 +3575,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3661,7 +3598,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -3670,19 +3607,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3693,7 +3630,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
@@ -3702,19 +3639,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3725,7 +3662,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
@@ -3734,19 +3671,19 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3757,7 +3694,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -3766,19 +3703,19 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3789,7 +3726,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -3810,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3860,7 +3797,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3892,22 +3829,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920345</v>
+        <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3915,19 +3852,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920345</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -3938,19 +3875,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920341</v>
+        <v>20330051920354</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -3961,185 +3898,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920381</v>
+        <v>20330051920354</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920347</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920349</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920350</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330050470596</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920356</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920357</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920383</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
